--- a/test-data/test1-esp-eu-mixto.xlsx
+++ b/test-data/test1-esp-eu-mixto.xlsx
@@ -121,10 +121,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
+        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
+        <a:font script="Hans" typeface="å®ä½"/>
+        <a:font script="Hant" typeface="æ°ç´°æé«"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -156,10 +156,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
+        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
+        <a:font script="Hans" typeface="å®ä½"/>
+        <a:font script="Hant" typeface="æ°ç´°æé«"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -404,7 +404,7 @@
         <v>CODIGO ESTABLECIMIENTO</v>
       </c>
       <c r="B1" t="str">
-        <v>12345</v>
+        <v>0000004630</v>
       </c>
     </row>
     <row r="2">
